--- a/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
+++ b/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,11 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font/>
+    <font>
+      <b val="1"/>
+      <color rgb="00D92D20"/>
     </font>
   </fonts>
   <fills count="3">
@@ -74,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -83,6 +88,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -459,6 +477,9 @@
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -516,6 +537,21 @@
           <t>언제 · 얼마나 자주</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>보조 문구</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>질문 글자 수</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>가장 긴 선택지</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -556,6 +592,13 @@
           <t>진료정보에 확인 안 된 질환이 있는 날, 첫 질문</t>
         </is>
       </c>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -596,6 +639,13 @@
           <t>매일. 질환 확인 질문이 없는 날, 또는 그 답이 「아니요 · 모르겠어요」인 날</t>
         </is>
       </c>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -636,6 +686,13 @@
           <t>자정~오전 10시</t>
         </is>
       </c>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -676,6 +733,13 @@
           <t>오전 10~12시</t>
         </is>
       </c>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -716,6 +780,13 @@
           <t>낮 12시~오후 2시</t>
         </is>
       </c>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -736,25 +807,32 @@
           <t>점심은 언제쯤 드셨어요?</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>오후 1:00 이후</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>12:00~1:00</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>12:00 이전</t>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>오후 1시 이후</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>12시~1시 사이</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>12시 이전</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
           <t>오후 2~5시</t>
         </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -796,6 +874,13 @@
           <t>오후 5~9시</t>
         </is>
       </c>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -836,6 +921,13 @@
           <t>오후 9시~자정</t>
         </is>
       </c>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -876,6 +968,13 @@
           <t>모든 끼니</t>
         </is>
       </c>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -916,6 +1015,13 @@
           <t>모든 끼니</t>
         </is>
       </c>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -956,6 +1062,13 @@
           <t>모든 끼니. 국물이 없던 끼니도 「먹지 않음」</t>
         </is>
       </c>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -996,6 +1109,13 @@
           <t>오전 4~10시에 들어온 날만</t>
         </is>
       </c>
+      <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1036,6 +1156,13 @@
           <t>모든 끼니</t>
         </is>
       </c>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1076,6 +1203,13 @@
           <t>모든 끼니</t>
         </is>
       </c>
+      <c r="I18" s="4" t="inlineStr"/>
+      <c r="J18" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1116,6 +1250,13 @@
           <t>모든 끼니</t>
         </is>
       </c>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1131,30 +1272,41 @@
           <t>운동 (최근 7일)</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>최근 7일, 숨이 조금 찰 만큼 움직인 시간은 모두 얼마나 됐나요?</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>90분보다 적었어요</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>90~150분 정도였어요</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>150분보다 많았어요</t>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 조금 찰 만큼 모두 몇 분 움직이셨어요?</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>90분 미만</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>90~150분</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>150분 넘게</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
           <t>하루 1개 · 7일에 2개까지. 위에서부터 먼저 물음. 같은 질문은 7일 뒤에 다시 물음</t>
         </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>예) 빠르게 걷기 · 자전거 · 계단 오르기</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -1171,9 +1323,9 @@
           <t>운동 (최근 7일)</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>최근 7일, 숨이 조금 찰 만큼 움직인 날이 며칠 있었나요?</t>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 조금 찰 만큼 움직인 날은 며칠인가요?</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1181,20 +1333,31 @@
           <t>없었어요</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>1~2일 있었어요</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>3일 이상 있었어요</t>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>1~2일</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>3일 이상</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
           <t>하루 1개 · 7일에 2개까지. 위에서부터 먼저 물음. 같은 질문은 7일 뒤에 다시 물음</t>
         </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>예) 빠르게 걷기 · 자전거 · 계단 오르기</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -1211,30 +1374,41 @@
           <t>운동 (최근 7일)</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>어제 숨이 조금 찰 만큼 움직인 시간은 얼마나 됐나요?</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>10분보다 적었어요</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>10분 이상 30분 미만이었어요</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>30분 이상이었어요</t>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>어제는 숨이 조금 찰 만큼 몇 분 움직이셨어요?</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>10분 미만</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>10~30분</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>30분 이상</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
           <t>하루 1개 · 7일에 2개까지. 위에서부터 먼저 물음. 같은 질문은 7일 뒤에 다시 물음</t>
         </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>예) 빠르게 걷기 · 자전거 · 계단 오르기</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -1251,30 +1425,41 @@
           <t>운동 (최근 7일)</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>최근 7일, 숨이 많이 찰 만큼 운동한 시간은 모두 얼마나 됐나요?</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>전혀 하지 않았어요</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>150분 이내로 했어요</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>150분보다 많았어요</t>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 많이 찰 만큼 모두 몇 분 운동하셨어요?</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>안 했어요</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>150분 이하</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>150분 넘게</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
           <t>하루 1개 · 7일에 2개까지. 위에서부터 먼저 물음. 같은 질문은 7일 뒤에 다시 물음</t>
         </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>예) 달리기 · 등산 · 수영</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1291,9 +1476,9 @@
           <t>운동 (최근 7일)</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>최근 7일, 근육을 쓰는 운동을 한 날이 며칠 있었나요?</t>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>최근 7일, 근력 운동을 한 날은 며칠이었나요?</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1301,20 +1486,31 @@
           <t>없었어요</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>1일 있었어요</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>2일 이상 있었어요</t>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>2일 이상</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
           <t>하루 1개 · 7일에 2개까지. 위에서부터 먼저 물음. 같은 질문은 7일 뒤에 다시 물음</t>
         </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>예) 스쿼트 · 아령 · 팔굽혀펴기</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1331,30 +1527,41 @@
           <t>운동 (최근 7일)</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>최근 7일, 근육을 쓰는 운동을 몇 번 했나요?</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>0~1번 했어요</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>2~3번 했어요</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>4번 이상 했어요</t>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>최근 7일, 근력 운동은 몇 번 하셨어요?</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>1번 이하</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>2~3번</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>4번 이상</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
           <t>하루 1개 · 7일에 2개까지. 위에서부터 먼저 물음. 같은 질문은 7일 뒤에 다시 물음</t>
         </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>예) 스쿼트 · 아령 · 팔굽혀펴기</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1371,30 +1578,41 @@
           <t>운동 (최근 7일)</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>최근 7일, 걷거나 운동한 시간은 평소의 절반과 비교해 어땠나요?</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>평소의 절반보다 적었어요</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>평소보다 적었지만 절반 이상이었어요</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>평소와 비슷하거나 더 많았어요</t>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>최근 7일, 평소와 비교해 얼마나 움직이셨어요?</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>반도 안 돼요</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>조금 줄었어요</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>줄지 않았어요</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
           <t>하루 1개 · 7일에 2개까지. 위에서부터 먼저 물음. 같은 질문은 7일 뒤에 다시 물음</t>
         </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>걷기와 운동을 모두 합쳐 생각해 주세요</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -1411,30 +1629,37 @@
           <t>수면 (어젯밤)</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>어젯밤 잠은 몇 시간 정도 주무셨나요?</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>7시간보다 적었어요</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>7~9시간 정도였어요</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>9시간보다 길었어요</t>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>어젯밤엔 몇 시간 주무셨어요?</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>7시간 미만</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>7~9시간</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>9시간 넘게</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
           <t>하루 1개. 매일 물을 수 있음</t>
         </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -1451,30 +1676,37 @@
           <t>수면 (최근 3일)</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>최근 3일, 잠든 시간과 일어난 시간이 얼마나 비슷했나요?</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>대체로 비슷했어요</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>1~2시간쯤 달랐어요</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>2시간 이상 달랐어요</t>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>최근 3일, 자고 일어나는 시각이 날마다 얼마나 달랐나요?</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>거의 같아요</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>1~2시간</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>2시간 이상</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
           <t>3일 뒤에 다시 물음 · 7일에 2번까지</t>
         </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr"/>
+      <c r="J28" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -1491,30 +1723,37 @@
           <t>수면 (최근 7일)</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>최근 7일, 하루에 잠은 대체로 몇 시간 잤나요?</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>7시간보다 적었어요</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>7~9시간 정도였어요</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>9시간보다 길었어요</t>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>최근 7일, 보통 몇 시간 주무셨어요?</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>7시간 미만</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>7~9시간</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>9시간 넘게</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
           <t>하루 1개 · 7일에 2개까지. 위에서부터 먼저 물음. 같은 질문은 7일 뒤에 다시 물음</t>
         </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr"/>
+      <c r="J29" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -1531,30 +1770,37 @@
           <t>수면 (최근 7일)</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>최근 7일, 잠잔 시간은 날마다 얼마나 달랐나요?</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>대체로 비슷했어요</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>1~2시간쯤 달랐어요</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>2시간 이상 달랐어요</t>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>최근 7일, 주무신 시간이 날마다 얼마나 달랐나요?</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>거의 같아요</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>1~2시간</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>2시간 이상</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
           <t>하루 1개 · 7일에 2개까지. 위에서부터 먼저 물음. 같은 질문은 7일 뒤에 다시 물음</t>
         </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr"/>
+      <c r="J30" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -1571,14 +1817,14 @@
           <t>피로감</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>오늘은 피로감이 어느 정도인가요?</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>전혀 피곤하지 않아요</t>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>오늘은 얼마나 피곤하세요?</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>괜찮아요</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1596,7 +1842,15 @@
           <t>하루 1개 · 7일에 4번까지</t>
         </is>
       </c>
-    </row>
+      <c r="I31" s="4" t="inlineStr"/>
+      <c r="J31" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -1604,6 +1858,22 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>화면 한도: 질문 카드 32자(2줄 × 16자) · 답 버튼 7자 · 보조 문구 1줄. 글자 수는 빈칸에 가장 긴 말(어제 저녁 · 이상지질혈증)을 넣어 셈. 예외: 「적게 · 몇 입만」「못 먹거나 거름」「조금/많이 배불렀어요」(식이 계약 확정 문구), 점심 오후 2시 뒤 시각 선택지(시각을 두 줄로 보여 줌)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>빨간 글씨: 지식DB 원문에서 화면에 맞게 바뀐 곳(뜻·경계값은 같음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
+++ b/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="질문과 선택지" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="식이 목표 문구" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="활동·수면 목표 문구" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="바뀐 내용" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="식이 목표 문구" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="활동·수면 목표 문구" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -79,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -101,6 +102,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -466,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -496,6 +498,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -809,7 +812,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>오후 1시 이후</t>
+          <t>1시 이후</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1872,14 +1875,684 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>바뀐 내용 · 기존 문구 → 바꾼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-16 · 보완 질문은 경계값(90분 · 150분 · 7시간 등)이 같아 계산은 그대로. 빨간 글씨가 바꾼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>기존 질문</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>기존 선택지</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>바꾼 질문</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>바꾼 선택지</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>보조 문구 · 비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 운동</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 조금 찰 만큼 움직인 시간은 모두 얼마나 됐나요?</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>90분보다 적었어요 / 90~150분 정도였어요 / 150분보다 많았어요</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 조금 찰 만큼 모두 몇 분 움직이셨어요?</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>90분 미만 / 90~150분 / 150분 넘게</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>예) 빠르게 걷기 · 자전거 · 계단 오르기</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 운동</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 조금 찰 만큼 움직인 날이 며칠 있었나요?</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>없었어요 / 1~2일 있었어요 / 3일 이상 있었어요</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 조금 찰 만큼 움직인 날은 며칠인가요?</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>없었어요 / 1~2일 / 3일 이상</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>예) 빠르게 걷기 · 자전거 · 계단 오르기</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 운동</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>어제 숨이 조금 찰 만큼 움직인 시간은 얼마나 됐나요?</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>10분보다 적었어요 / 10분 이상 30분 미만이었어요 / 30분 이상이었어요</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>어제는 숨이 조금 찰 만큼 몇 분 움직이셨어요?</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>10분 미만 / 10~30분 / 30분 이상</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>예) 빠르게 걷기 · 자전거 · 계단 오르기</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 운동</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 많이 찰 만큼 운동한 시간은 모두 얼마나 됐나요?</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>전혀 하지 않았어요 / 150분 이내로 했어요 / 150분보다 많았어요</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 많이 찰 만큼 모두 몇 분 운동하셨어요?</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>안 했어요 / 150분 이하 / 150분 넘게</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>예) 달리기 · 등산 · 수영</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 운동</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>최근 7일, 근육을 쓰는 운동을 한 날이 며칠 있었나요?</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>없었어요 / 1일 있었어요 / 2일 이상 있었어요</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>최근 7일, 근력 운동을 한 날은 며칠이었나요?</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>없었어요 / 1일 / 2일 이상</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>예) 스쿼트 · 아령 · 팔굽혀펴기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 운동</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>최근 7일, 근육을 쓰는 운동을 몇 번 했나요?</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>0~1번 했어요 / 2~3번 했어요 / 4번 이상 했어요</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>최근 7일, 근력 운동은 몇 번 하셨어요?</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>1번 이하 / 2~3번 / 4번 이상</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>예) 스쿼트 · 아령 · 팔굽혀펴기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 운동</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>최근 7일, 걷거나 운동한 시간은 평소의 절반과 비교해 어땠나요?</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>평소의 절반보다 적었어요 / 평소보다 적었지만 절반 이상이었어요 / 평소와 비슷하거나 더 많았어요</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>최근 7일, 평소와 비교해 얼마나 움직이셨어요?</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>반도 안 돼요 / 조금 줄었어요 / 줄지 않았어요</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>걷기와 운동을 모두 합쳐 생각해 주세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 수면</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>어젯밤 잠은 몇 시간 정도 주무셨나요?</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>7시간보다 적었어요 / 7~9시간 정도였어요 / 9시간보다 길었어요</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>어젯밤엔 몇 시간 주무셨어요?</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>7시간 미만 / 7~9시간 / 9시간 넘게</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 수면</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>최근 3일, 잠든 시간과 일어난 시간이 얼마나 비슷했나요?</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>대체로 비슷했어요 / 1~2시간쯤 달랐어요 / 2시간 이상 달랐어요</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>최근 3일, 자고 일어나는 시각이 날마다 얼마나 달랐나요?</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>거의 같아요 / 1~2시간 / 2시간 이상</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 수면</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>최근 7일, 하루에 잠은 대체로 몇 시간 잤나요?</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>7시간보다 적었어요 / 7~9시간 정도였어요 / 9시간보다 길었어요</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>최근 7일, 보통 몇 시간 주무셨어요?</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>7시간 미만 / 7~9시간 / 9시간 넘게</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 수면</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>최근 7일, 잠잔 시간은 날마다 얼마나 달랐나요?</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>대체로 비슷했어요 / 1~2시간쯤 달랐어요 / 2시간 이상 달랐어요</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>최근 7일, 주무신 시간이 날마다 얼마나 달랐나요?</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>거의 같아요 / 1~2시간 / 2시간 이상</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 피로감</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>오늘은 피로감이 어느 정도인가요?</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>전혀 피곤하지 않아요 / 조금 피곤해요 / 많이 피곤해요</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>오늘은 얼마나 피곤하세요?</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>괜찮아요 / 조금 피곤해요 / 많이 피곤해요</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>프로토타입 · 피로감</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>오늘 몸의 피로감은 어느 정도인가요?</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>괜찮아요 / 조금 피곤해요 / 많이 피곤해요</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>오늘은 얼마나 피곤하세요?</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>괜찮아요 / 조금 피곤해요 / 많이 피곤해요</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>프로토타입 · 수면</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>어젯밤 얼마나 주무셨나요?</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>5시간 미만 / 5~7시간 / 7시간 이상</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>어젯밤엔 몇 시간 주무셨어요?</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>7시간 미만 / 7~9시간 / 9시간 넘게</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>수면 기준 5시간 → 7시간. 「일찍 누워 보세요」 코칭도 7시간 미만부터</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>식사 시각 · 점심 (오후 2시 뒤)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>점심은 언제쯤 드셨어요?</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>오후 1:00 이후 / 12:00~1:00 / 12:00 이전</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>점심은 언제쯤 드셨어요? (그대로)</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>1시 이후 / 12시~1시 사이 / 12시 이전</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>식사 시각 · 점심 (낮 12시대)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>점심은 언제쯤 드셨어요?</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>오후 12:00 이후 / 오전~오후 11:00~12:00 / 오전 11:00 이전</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>점심은 언제쯤 드셨어요? (그대로)</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>12시 이후 / 11시~12시 사이 / 11시 이전</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>제안 · 식이 (적용 안 함)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>{지난 끼니} 전후 단 음료·간식은 몇 번이었나요?</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>없었어요 / 한 번 / 두 번 이상</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>{지난 끼니} 전후 단 음료나 간식은 몇 번이었나요?</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>그대로</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>「·」에서 줄이 끊김</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>제안 · 식이 (적용 안 함)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>{지난 끼니}엔 단백질류(고기·생선·달걀 등)를 드셨나요?</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>먹었어요 / 맛만 봤어요 / 안 먹었어요</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>{지난 끼니}엔 고기나 생선, 달걀, 두부를 드셨나요?</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>그대로</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>「·」에서 줄이 끊김</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1912,6 +2585,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -17959,7 +18633,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17989,6 +18663,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>

--- a/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
+++ b/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
@@ -80,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -103,6 +103,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -468,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -498,7 +501,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1279,7 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>최근 7일, 숨이 조금 찰 만큼 모두 몇 분 움직이셨어요?</t>
+          <t>최근 7일, 숨이 조금 찰 정도로 움직인 시간은 모두 얼마나 되나요?</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1306,7 +1308,7 @@
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>7</v>
@@ -1328,10 +1330,10 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>최근 7일, 숨이 조금 찰 만큼 움직인 날은 며칠인가요?</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
+          <t>최근 7일, 숨이 조금 찰 정도로 움직인 날은 며칠이었나요?</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>없었어요</t>
         </is>
@@ -1357,7 +1359,7 @@
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K21" s="5" t="n">
         <v>5</v>
@@ -1379,7 +1381,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>어제는 숨이 조금 찰 만큼 몇 분 움직이셨어요?</t>
+          <t>어제는 숨이 조금 찰 정도로 몇 분쯤 움직이셨나요?</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1408,7 +1410,7 @@
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>6</v>
@@ -1430,12 +1432,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>최근 7일, 숨이 많이 찰 만큼 모두 몇 분 운동하셨어요?</t>
+          <t>최근 7일, 숨이 많이 찰 정도로 운동한 시간은 모두 얼마나 되나요?</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>안 했어요</t>
+          <t>하지 않았어요</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -1459,7 +1461,7 @@
         </is>
       </c>
       <c r="J23" s="5" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K23" s="5" t="n">
         <v>7</v>
@@ -1484,7 +1486,7 @@
           <t>최근 7일, 근력 운동을 한 날은 며칠이었나요?</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>없었어요</t>
         </is>
@@ -1532,7 +1534,7 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>최근 7일, 근력 운동은 몇 번 하셨어요?</t>
+          <t>최근 7일, 근력 운동은 몇 번 하셨나요?</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1583,22 +1585,22 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>최근 7일, 평소와 비교해 얼마나 움직이셨어요?</t>
+          <t>최근 7일, 걷거나 운동한 시간은 평소와 비교해 어땠나요?</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>반도 안 돼요</t>
+          <t>절반도 안 됐어요</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>조금 줄었어요</t>
+          <t>조금 적었어요</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>줄지 않았어요</t>
+          <t>평소만큼 했어요</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -1612,10 +1614,10 @@
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -1634,7 +1636,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>어젯밤엔 몇 시간 주무셨어요?</t>
+          <t>어젯밤에는 몇 시간 주무셨나요?</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1659,7 +1661,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr"/>
       <c r="J27" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" s="5" t="n">
         <v>6</v>
@@ -1681,17 +1683,17 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>최근 3일, 자고 일어나는 시각이 날마다 얼마나 달랐나요?</t>
+          <t>최근 3일, 잠들고 일어나는 시간은 날마다 얼마나 달랐나요?</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>거의 같아요</t>
+          <t>거의 같았어요</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>1~2시간</t>
+          <t>1~2시간 정도</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -1706,10 +1708,10 @@
       </c>
       <c r="I28" s="4" t="inlineStr"/>
       <c r="J28" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -1728,7 +1730,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>최근 7일, 보통 몇 시간 주무셨어요?</t>
+          <t>최근 7일, 하루에 보통 몇 시간 주무셨나요?</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1753,7 +1755,7 @@
       </c>
       <c r="I29" s="4" t="inlineStr"/>
       <c r="J29" s="5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K29" s="5" t="n">
         <v>6</v>
@@ -1775,17 +1777,17 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>최근 7일, 주무신 시간이 날마다 얼마나 달랐나요?</t>
+          <t>최근 7일, 주무신 시간은 날마다 얼마나 달랐나요?</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>거의 같아요</t>
+          <t>거의 같았어요</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>1~2시간</t>
+          <t>1~2시간 정도</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -1803,7 +1805,7 @@
         <v>28</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -1822,20 +1824,20 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>오늘은 얼마나 피곤하세요?</t>
+          <t>오늘은 몸이 얼마나 피곤하신가요?</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>괜찮아요</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
+          <t>피곤하지 않아요</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>조금 피곤해요</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>많이 피곤해요</t>
         </is>
@@ -1847,10 +1849,10 @@
       </c>
       <c r="I31" s="4" t="inlineStr"/>
       <c r="J31" s="5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32"/>
@@ -1864,7 +1866,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>화면 한도: 질문 카드 32자(2줄 × 16자) · 답 버튼 7자 · 보조 문구 1줄. 글자 수는 빈칸에 가장 긴 말(어제 저녁 · 이상지질혈증)을 넣어 셈. 예외: 「적게 · 몇 입만」「못 먹거나 거름」「조금/많이 배불렀어요」(식이 계약 확정 문구), 점심 오후 2시 뒤 시각 선택지(시각을 두 줄로 보여 줌)</t>
+          <t>화면 한도: 질문 카드 2줄(약 40자) · 답 버튼 1줄(약 9자). 프로토타입 질문 카드에서 확인. 글자 수는 빈칸에 가장 긴 말(어제 저녁 · 이상지질혈증)을 넣어 셈</t>
         </is>
       </c>
     </row>
@@ -1875,6 +1877,10 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1886,7 +1892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1970,7 +1976,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>최근 7일, 숨이 조금 찰 만큼 모두 몇 분 움직이셨어요?</t>
+          <t>최근 7일, 숨이 조금 찰 정도로 움직인 시간은 모두 얼마나 되나요?</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -2005,7 +2011,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>최근 7일, 숨이 조금 찰 만큼 움직인 날은 며칠인가요?</t>
+          <t>최근 7일, 숨이 조금 찰 정도로 움직인 날은 며칠이었나요?</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -2040,7 +2046,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>어제는 숨이 조금 찰 만큼 몇 분 움직이셨어요?</t>
+          <t>어제는 숨이 조금 찰 정도로 몇 분쯤 움직이셨나요?</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -2075,12 +2081,12 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>최근 7일, 숨이 많이 찰 만큼 모두 몇 분 운동하셨어요?</t>
+          <t>최근 7일, 숨이 많이 찰 정도로 운동한 시간은 모두 얼마나 되나요?</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>안 했어요 / 150분 이하 / 150분 넘게</t>
+          <t>하지 않았어요 / 150분 이하 / 150분 넘게</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -2145,7 +2151,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>최근 7일, 근력 운동은 몇 번 하셨어요?</t>
+          <t>최근 7일, 근력 운동은 몇 번 하셨나요?</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -2180,12 +2186,12 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>최근 7일, 평소와 비교해 얼마나 움직이셨어요?</t>
+          <t>최근 7일, 걷거나 운동한 시간은 평소와 비교해 어땠나요?</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>반도 안 돼요 / 조금 줄었어요 / 줄지 않았어요</t>
+          <t>절반도 안 됐어요 / 조금 적었어요 / 평소만큼 했어요</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -2215,7 +2221,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>어젯밤엔 몇 시간 주무셨어요?</t>
+          <t>어젯밤에는 몇 시간 주무셨나요?</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -2246,12 +2252,12 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>최근 3일, 자고 일어나는 시각이 날마다 얼마나 달랐나요?</t>
+          <t>최근 3일, 잠들고 일어나는 시간은 날마다 얼마나 달랐나요?</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>거의 같아요 / 1~2시간 / 2시간 이상</t>
+          <t>거의 같았어요 / 1~2시간 정도 / 2시간 이상</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -2277,7 +2283,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>최근 7일, 보통 몇 시간 주무셨어요?</t>
+          <t>최근 7일, 하루에 보통 몇 시간 주무셨나요?</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -2308,12 +2314,12 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>최근 7일, 주무신 시간이 날마다 얼마나 달랐나요?</t>
+          <t>최근 7일, 주무신 시간은 날마다 얼마나 달랐나요?</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>거의 같아요 / 1~2시간 / 2시간 이상</t>
+          <t>거의 같았어요 / 1~2시간 정도 / 2시간 이상</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -2339,12 +2345,12 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>오늘은 얼마나 피곤하세요?</t>
+          <t>오늘은 몸이 얼마나 피곤하신가요?</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>괜찮아요 / 조금 피곤해요 / 많이 피곤해요</t>
+          <t>피곤하지 않아요 / 조금 피곤해요 / 많이 피곤해요</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -2370,12 +2376,12 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>오늘은 얼마나 피곤하세요?</t>
+          <t>오늘은 몸이 얼마나 피곤하신가요?</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>괜찮아요 / 조금 피곤해요 / 많이 피곤해요</t>
+          <t>피곤하지 않아요 / 조금 피곤해요 / 많이 피곤해요</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -2401,7 +2407,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>어젯밤엔 몇 시간 주무셨어요?</t>
+          <t>어젯밤에는 몇 시간 주무셨나요?</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -2547,6 +2553,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2585,7 +2592,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -18663,7 +18669,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>

--- a/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
+++ b/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1855,7 +1855,6 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -1877,10 +1876,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1892,7 +1887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2361,27 +2356,27 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>프로토타입 · 피로감</t>
+          <t>식사 시각 · 점심 (오후 2시 뒤)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>오늘 몸의 피로감은 어느 정도인가요?</t>
+          <t>점심은 언제쯤 드셨어요?</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>괜찮아요 / 조금 피곤해요 / 많이 피곤해요</t>
+          <t>오후 1:00 이후 / 12:00~1:00 / 12:00 이전</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>오늘은 몸이 얼마나 피곤하신가요?</t>
+          <t>점심은 언제쯤 드셨어요? (그대로)</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>피곤하지 않아요 / 조금 피곤해요 / 많이 피곤해요</t>
+          <t>1시 이후 / 12시~1시 사이 / 12시 이전</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -2392,34 +2387,30 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>프로토타입 · 수면</t>
+          <t>식사 시각 · 점심 (낮 12시대)</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>어젯밤 얼마나 주무셨나요?</t>
+          <t>점심은 언제쯤 드셨어요?</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>5시간 미만 / 5~7시간 / 7시간 이상</t>
+          <t>오후 12:00 이후 / 오전~오후 11:00~12:00 / 오전 11:00 이전</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>어젯밤에는 몇 시간 주무셨나요?</t>
+          <t>점심은 언제쯤 드셨어요? (그대로)</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>7시간 미만 / 7~9시간 / 9시간 넘게</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>수면 기준 5시간 → 7시간. 「일찍 누워 보세요」 코칭도 7시간 미만부터</t>
-        </is>
-      </c>
+          <t>12시 이후 / 11시~12시 사이 / 11시 이전</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -2427,30 +2418,34 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>식사 시각 · 점심 (오후 2시 뒤)</t>
+          <t>제안 · 식이 (적용 안 함)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>점심은 언제쯤 드셨어요?</t>
+          <t>{지난 끼니} 전후 단 음료·간식은 몇 번이었나요?</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>오후 1:00 이후 / 12:00~1:00 / 12:00 이전</t>
+          <t>없었어요 / 한 번 / 두 번 이상</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>점심은 언제쯤 드셨어요? (그대로)</t>
+          <t>{지난 끼니} 전후 단 음료나 간식은 몇 번이었나요?</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>1시 이후 / 12시~1시 사이 / 12시 이전</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr"/>
+          <t>그대로</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>「·」에서 줄이 끊김</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -2458,102 +2453,36 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>식사 시각 · 점심 (낮 12시대)</t>
+          <t>제안 · 식이 (적용 안 함)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>점심은 언제쯤 드셨어요?</t>
+          <t>{지난 끼니}엔 단백질류(고기·생선·달걀 등)를 드셨나요?</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>오후 12:00 이후 / 오전~오후 11:00~12:00 / 오전 11:00 이전</t>
+          <t>먹었어요 / 맛만 봤어요 / 안 먹었어요</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>점심은 언제쯤 드셨어요? (그대로)</t>
+          <t>{지난 끼니}엔 고기나 생선, 달걀, 두부를 드셨나요?</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>12시 이후 / 11시~12시 사이 / 11시 이전</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>제안 · 식이 (적용 안 함)</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>{지난 끼니} 전후 단 음료·간식은 몇 번이었나요?</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>없었어요 / 한 번 / 두 번 이상</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>{지난 끼니} 전후 단 음료나 간식은 몇 번이었나요?</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>「·」에서 줄이 끊김</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>제안 · 식이 (적용 안 함)</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>{지난 끼니}엔 단백질류(고기·생선·달걀 등)를 드셨나요?</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>먹었어요 / 맛만 봤어요 / 안 먹었어요</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>{지난 끼니}엔 고기나 생선, 달걀, 두부를 드셨나요?</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>「·」에서 줄이 끊김</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
+    <row r="21"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
+++ b/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
@@ -1333,9 +1333,9 @@
           <t>최근 7일, 숨이 조금 찰 정도로 움직인 날은 며칠이었나요?</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>없었어요</t>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>없음</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>하지 않았어요</t>
+          <t>안 함</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -1486,9 +1486,9 @@
           <t>최근 7일, 근력 운동을 한 날은 며칠이었나요?</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>없었어요</t>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>없음</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>절반도 안 됐어요</t>
+          <t>절반 미만</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>조금 적었어요</t>
+          <t>조금 적음</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>평소만큼 했어요</t>
+          <t>평소만큼</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -1617,7 +1617,7 @@
         <v>32</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>거의 같았어요</t>
+          <t>거의 같음</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>1~2시간 정도</t>
+          <t>1~2시간</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -1711,7 +1711,7 @@
         <v>33</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>거의 같았어요</t>
+          <t>거의 같음</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>1~2시간 정도</t>
+          <t>1~2시간</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -1805,7 +1805,7 @@
         <v>28</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -1829,17 +1829,17 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>피곤하지 않아요</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>조금 피곤해요</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr">
-        <is>
-          <t>많이 피곤해요</t>
+          <t>피곤하지 않음</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>조금 피곤함</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>많이 피곤함</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -1852,9 +1852,10 @@
         <v>18</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>8</v>
-      </c>
-    </row>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -1887,7 +1888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2011,7 +2012,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>없었어요 / 1~2일 / 3일 이상</t>
+          <t>없음 / 1~2일 / 3일 이상</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -2081,7 +2082,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>하지 않았어요 / 150분 이하 / 150분 넘게</t>
+          <t>안 함 / 150분 이하 / 150분 넘게</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -2116,7 +2117,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>없었어요 / 1일 / 2일 이상</t>
+          <t>없음 / 1일 / 2일 이상</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2186,7 +2187,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>절반도 안 됐어요 / 조금 적었어요 / 평소만큼 했어요</t>
+          <t>절반 미만 / 조금 적음 / 평소만큼</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -2252,7 +2253,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>거의 같았어요 / 1~2시간 정도 / 2시간 이상</t>
+          <t>거의 같음 / 1~2시간 / 2시간 이상</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -2314,7 +2315,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>거의 같았어요 / 1~2시간 정도 / 2시간 이상</t>
+          <t>거의 같음 / 1~2시간 / 2시간 이상</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -2345,7 +2346,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>피곤하지 않아요 / 조금 피곤해요 / 많이 피곤해요</t>
+          <t>피곤하지 않음 / 조금 피곤함 / 많이 피곤함</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -2412,77 +2413,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>제안 · 식이 (적용 안 함)</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>{지난 끼니} 전후 단 음료·간식은 몇 번이었나요?</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>없었어요 / 한 번 / 두 번 이상</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>{지난 끼니} 전후 단 음료나 간식은 몇 번이었나요?</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>「·」에서 줄이 끊김</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>제안 · 식이 (적용 안 함)</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>{지난 끼니}엔 단백질류(고기·생선·달걀 등)를 드셨나요?</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>먹었어요 / 맛만 봤어요 / 안 먹었어요</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>{지난 끼니}엔 고기나 생선, 달걀, 두부를 드셨나요?</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>「·」에서 줄이 끊김</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
+    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
+++ b/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
@@ -1277,9 +1277,9 @@
           <t>운동 (최근 7일)</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>최근 7일, 숨이 조금 찰 정도로 움직인 시간은 모두 얼마나 되나요?</t>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 조금 찰 만큼 움직인 시간은 모두 얼마나 됐나요?</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>7</v>
@@ -1328,9 +1328,9 @@
           <t>운동 (최근 7일)</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>최근 7일, 숨이 조금 찰 정도로 움직인 날은 며칠이었나요?</t>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 조금 찰 만큼 움직인 날이 며칠 있었나요?</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1379,9 +1379,9 @@
           <t>운동 (최근 7일)</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>어제는 숨이 조금 찰 정도로 몇 분쯤 움직이셨나요?</t>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>어제 숨이 조금 찰 만큼 움직인 시간은 얼마나 됐나요?</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>6</v>
@@ -1430,9 +1430,9 @@
           <t>운동 (최근 7일)</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>최근 7일, 숨이 많이 찰 정도로 운동한 시간은 모두 얼마나 되나요?</t>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 많이 찰 만큼 운동한 시간은 모두 얼마나 됐나요?</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="J23" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K23" s="5" t="n">
         <v>7</v>
@@ -1481,9 +1481,9 @@
           <t>운동 (최근 7일)</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>최근 7일, 근력 운동을 한 날은 며칠이었나요?</t>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>최근 7일, 근육을 쓰는 운동을 한 날이 며칠 있었나요?</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="J24" s="5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>5</v>
@@ -1532,9 +1532,9 @@
           <t>운동 (최근 7일)</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>최근 7일, 근력 운동은 몇 번 하셨나요?</t>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>최근 7일, 근육을 쓰는 운동을 몇 번 했나요?</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="J25" s="5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K25" s="5" t="n">
         <v>5</v>
@@ -1583,9 +1583,9 @@
           <t>운동 (최근 7일)</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>최근 7일, 걷거나 운동한 시간은 평소와 비교해 어땠나요?</t>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>최근 7일, 걷거나 운동한 시간은 평소의 절반과 비교해 어땠나요?</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>조금 적음</t>
+          <t>절반~평소</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>평소만큼</t>
+          <t>평소 이상</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>5</v>
@@ -1634,9 +1634,9 @@
           <t>수면 (어젯밤)</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>어젯밤에는 몇 시간 주무셨나요?</t>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>어젯밤 잠은 몇 시간 정도 주무셨나요?</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr"/>
       <c r="J27" s="5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K27" s="5" t="n">
         <v>6</v>
@@ -1681,9 +1681,9 @@
           <t>수면 (최근 3일)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>최근 3일, 잠들고 일어나는 시간은 날마다 얼마나 달랐나요?</t>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>최근 3일, 잠든 시간과 일어난 시간이 얼마나 비슷했나요?</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="I28" s="4" t="inlineStr"/>
       <c r="J28" s="5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K28" s="5" t="n">
         <v>6</v>
@@ -1728,9 +1728,9 @@
           <t>수면 (최근 7일)</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>최근 7일, 하루에 보통 몇 시간 주무셨나요?</t>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>최근 7일, 하루에 잠은 대체로 몇 시간 잤나요?</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="I29" s="4" t="inlineStr"/>
       <c r="J29" s="5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K29" s="5" t="n">
         <v>6</v>
@@ -1775,9 +1775,9 @@
           <t>수면 (최근 7일)</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>최근 7일, 주무신 시간은 날마다 얼마나 달랐나요?</t>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>최근 7일, 잠잔 시간은 날마다 얼마나 달랐나요?</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="I30" s="4" t="inlineStr"/>
       <c r="J30" s="5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K30" s="5" t="n">
         <v>6</v>
@@ -1822,9 +1822,9 @@
           <t>피로감</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>오늘은 몸이 얼마나 피곤하신가요?</t>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>오늘은 피로감이 어느 정도인가요?</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1970,9 +1970,9 @@
           <t>90분보다 적었어요 / 90~150분 정도였어요 / 150분보다 많았어요</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>최근 7일, 숨이 조금 찰 정도로 움직인 시간은 모두 얼마나 되나요?</t>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>그대로</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -2005,9 +2005,9 @@
           <t>없었어요 / 1~2일 있었어요 / 3일 이상 있었어요</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>최근 7일, 숨이 조금 찰 정도로 움직인 날은 며칠이었나요?</t>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>그대로</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -2040,9 +2040,9 @@
           <t>10분보다 적었어요 / 10분 이상 30분 미만이었어요 / 30분 이상이었어요</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>어제는 숨이 조금 찰 정도로 몇 분쯤 움직이셨나요?</t>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>그대로</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -2075,9 +2075,9 @@
           <t>전혀 하지 않았어요 / 150분 이내로 했어요 / 150분보다 많았어요</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>최근 7일, 숨이 많이 찰 정도로 운동한 시간은 모두 얼마나 되나요?</t>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>그대로</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -2110,9 +2110,9 @@
           <t>없었어요 / 1일 있었어요 / 2일 이상 있었어요</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>최근 7일, 근력 운동을 한 날은 며칠이었나요?</t>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>그대로</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -2145,9 +2145,9 @@
           <t>0~1번 했어요 / 2~3번 했어요 / 4번 이상 했어요</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>최근 7일, 근력 운동은 몇 번 하셨나요?</t>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>그대로</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -2180,14 +2180,14 @@
           <t>평소의 절반보다 적었어요 / 평소보다 적었지만 절반 이상이었어요 / 평소와 비슷하거나 더 많았어요</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>최근 7일, 걷거나 운동한 시간은 평소와 비교해 어땠나요?</t>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>그대로</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>절반 미만 / 조금 적음 / 평소만큼</t>
+          <t>절반 미만 / 절반~평소 / 평소 이상</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -2215,9 +2215,9 @@
           <t>7시간보다 적었어요 / 7~9시간 정도였어요 / 9시간보다 길었어요</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>어젯밤에는 몇 시간 주무셨나요?</t>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>그대로</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -2246,9 +2246,9 @@
           <t>대체로 비슷했어요 / 1~2시간쯤 달랐어요 / 2시간 이상 달랐어요</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>최근 3일, 잠들고 일어나는 시간은 날마다 얼마나 달랐나요?</t>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>그대로</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -2277,9 +2277,9 @@
           <t>7시간보다 적었어요 / 7~9시간 정도였어요 / 9시간보다 길었어요</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>최근 7일, 하루에 보통 몇 시간 주무셨나요?</t>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>그대로</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -2308,9 +2308,9 @@
           <t>대체로 비슷했어요 / 1~2시간쯤 달랐어요 / 2시간 이상 달랐어요</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>최근 7일, 주무신 시간은 날마다 얼마나 달랐나요?</t>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>그대로</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -2339,9 +2339,9 @@
           <t>전혀 피곤하지 않아요 / 조금 피곤해요 / 많이 피곤해요</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>오늘은 몸이 얼마나 피곤하신가요?</t>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>그대로</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">

--- a/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
+++ b/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="질문과 선택지" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="바뀐 내용" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="바뀐 내용" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="질문과 선택지" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="식이 목표 문구" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="활동·수면 목표 문구" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
@@ -471,6 +471,543 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>바뀐 내용 · 기존 문구 → 바꾼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-16 · 보완 질문은 경계값(90분 · 150분 · 7시간 등)이 같아 계산은 그대로. 빨간 글씨가 바꾼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>기존 질문</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>기존 선택지</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>바꾼 질문</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>바꾼 선택지</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>보조 문구 · 비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 운동</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 조금 찰 만큼 움직인 시간은 모두 얼마나 됐나요?</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>90분보다 적었어요 / 90~150분 정도였어요 / 150분보다 많았어요</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 조금 찰 만큼 움직인 시간은 모두 얼마나 됐나요?</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>90분 미만 / 90~150분 / 150분 넘게</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>예) 빠르게 걷기 · 자전거 · 계단 오르기</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 운동</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 조금 찰 만큼 움직인 날이 며칠 있었나요?</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>없었어요 / 1~2일 있었어요 / 3일 이상 있었어요</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 조금 찰 만큼 움직인 날이 며칠 있었나요?</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>없음 / 1~2일 / 3일 이상</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>예) 빠르게 걷기 · 자전거 · 계단 오르기</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 운동</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>어제 숨이 조금 찰 만큼 움직인 시간은 얼마나 됐나요?</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>10분보다 적었어요 / 10분 이상 30분 미만이었어요 / 30분 이상이었어요</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>어제 숨이 조금 찰 만큼 움직인 시간은 얼마나 됐나요?</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>10분 미만 / 10~30분 / 30분 이상</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>예) 빠르게 걷기 · 자전거 · 계단 오르기</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 운동</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 많이 찰 만큼 운동한 시간은 모두 얼마나 됐나요?</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>전혀 하지 않았어요 / 150분 이내로 했어요 / 150분보다 많았어요</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 많이 찰 만큼 운동한 시간은 모두 얼마나 됐나요?</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>안 함 / 150분 이하 / 150분 넘게</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>예) 달리기 · 등산 · 수영</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 운동</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>최근 7일, 근육을 쓰는 운동을 한 날이 며칠 있었나요?</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>없었어요 / 1일 있었어요 / 2일 이상 있었어요</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>최근 7일, 근육을 쓰는 운동을 한 날이 며칠 있었나요?</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>없음 / 1일 / 2일 이상</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>예) 스쿼트 · 아령 · 팔굽혀펴기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 운동</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>최근 7일, 근육을 쓰는 운동을 몇 번 했나요?</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>0~1번 했어요 / 2~3번 했어요 / 4번 이상 했어요</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>최근 7일, 근육을 쓰는 운동을 몇 번 했나요?</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>1번 이하 / 2~3번 / 4번 이상</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>예) 스쿼트 · 아령 · 팔굽혀펴기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 운동</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>최근 7일, 걷거나 운동한 시간은 평소의 절반과 비교해 어땠나요?</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>평소의 절반보다 적었어요 / 평소보다 적었지만 절반 이상이었어요 / 평소와 비슷하거나 더 많았어요</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>최근 7일, 걷거나 운동한 시간은 평소의 절반과 비교해 어땠나요?</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>절반 미만 / 절반~평소 / 평소 이상</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>걷기와 운동을 모두 합쳐 생각해 주세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 수면</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>어젯밤 잠은 몇 시간 정도 주무셨나요?</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>7시간보다 적었어요 / 7~9시간 정도였어요 / 9시간보다 길었어요</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>어젯밤 잠은 몇 시간 정도 주무셨나요?</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>7시간 미만 / 7~9시간 / 9시간 넘게</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 수면</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>최근 3일, 잠든 시간과 일어난 시간이 얼마나 비슷했나요?</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>대체로 비슷했어요 / 1~2시간쯤 달랐어요 / 2시간 이상 달랐어요</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>최근 3일, 잠든 시간과 일어난 시간이 얼마나 비슷했나요?</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>거의 같음 / 1~2시간 / 2시간 이상</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 수면</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>최근 7일, 하루에 잠은 대체로 몇 시간 잤나요?</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>7시간보다 적었어요 / 7~9시간 정도였어요 / 9시간보다 길었어요</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>최근 7일, 하루에 잠은 대체로 몇 시간 잤나요?</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>7시간 미만 / 7~9시간 / 9시간 넘게</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 수면</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>최근 7일, 잠잔 시간은 날마다 얼마나 달랐나요?</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>대체로 비슷했어요 / 1~2시간쯤 달랐어요 / 2시간 이상 달랐어요</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>최근 7일, 잠잔 시간은 날마다 얼마나 달랐나요?</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>거의 같음 / 1~2시간 / 2시간 이상</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>보완 · 피로감</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>오늘은 피로감이 어느 정도인가요?</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>전혀 피곤하지 않아요 / 조금 피곤해요 / 많이 피곤해요</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>오늘은 피로감이 어느 정도인가요?</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>피곤하지 않음 / 조금 피곤함 / 많이 피곤함</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>식사 시각 · 점심 (오후 2시 뒤)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>점심은 언제쯤 드셨어요?</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>오후 1:00 이후 / 12:00~1:00 / 12:00 이전</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>점심은 언제쯤 드셨어요? (그대로)</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>1시 이후 / 12시~1시 사이 / 12시 이전</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>식사 시각 · 점심 (낮 12시대)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>점심은 언제쯤 드셨어요?</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>오후 12:00 이후 / 오전~오후 11:00~12:00 / 오전 11:00 이전</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>점심은 언제쯤 드셨어요? (그대로)</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>12시 이후 / 11시~12시 사이 / 11시 이전</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1855,7 +2392,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -1877,543 +2413,6 @@
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>바뀐 내용 · 기존 문구 → 바꾼 문구</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-16 · 보완 질문은 경계값(90분 · 150분 · 7시간 등)이 같아 계산은 그대로. 빨간 글씨가 바꾼 문구</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>기존 질문</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>기존 선택지</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>바꾼 질문</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>바꾼 선택지</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>보조 문구 · 비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>보완 · 운동</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>최근 7일, 숨이 조금 찰 만큼 움직인 시간은 모두 얼마나 됐나요?</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>90분보다 적었어요 / 90~150분 정도였어요 / 150분보다 많았어요</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>90분 미만 / 90~150분 / 150분 넘게</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>예) 빠르게 걷기 · 자전거 · 계단 오르기</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>보완 · 운동</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>최근 7일, 숨이 조금 찰 만큼 움직인 날이 며칠 있었나요?</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>없었어요 / 1~2일 있었어요 / 3일 이상 있었어요</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>없음 / 1~2일 / 3일 이상</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>예) 빠르게 걷기 · 자전거 · 계단 오르기</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>보완 · 운동</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>어제 숨이 조금 찰 만큼 움직인 시간은 얼마나 됐나요?</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>10분보다 적었어요 / 10분 이상 30분 미만이었어요 / 30분 이상이었어요</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>10분 미만 / 10~30분 / 30분 이상</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>예) 빠르게 걷기 · 자전거 · 계단 오르기</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>보완 · 운동</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>최근 7일, 숨이 많이 찰 만큼 운동한 시간은 모두 얼마나 됐나요?</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>전혀 하지 않았어요 / 150분 이내로 했어요 / 150분보다 많았어요</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>안 함 / 150분 이하 / 150분 넘게</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>예) 달리기 · 등산 · 수영</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>보완 · 운동</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>최근 7일, 근육을 쓰는 운동을 한 날이 며칠 있었나요?</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>없었어요 / 1일 있었어요 / 2일 이상 있었어요</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>없음 / 1일 / 2일 이상</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>예) 스쿼트 · 아령 · 팔굽혀펴기</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>보완 · 운동</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>최근 7일, 근육을 쓰는 운동을 몇 번 했나요?</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>0~1번 했어요 / 2~3번 했어요 / 4번 이상 했어요</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>1번 이하 / 2~3번 / 4번 이상</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>예) 스쿼트 · 아령 · 팔굽혀펴기</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>보완 · 운동</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>최근 7일, 걷거나 운동한 시간은 평소의 절반과 비교해 어땠나요?</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>평소의 절반보다 적었어요 / 평소보다 적었지만 절반 이상이었어요 / 평소와 비슷하거나 더 많았어요</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>절반 미만 / 절반~평소 / 평소 이상</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>걷기와 운동을 모두 합쳐 생각해 주세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>보완 · 수면</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>어젯밤 잠은 몇 시간 정도 주무셨나요?</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>7시간보다 적었어요 / 7~9시간 정도였어요 / 9시간보다 길었어요</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>7시간 미만 / 7~9시간 / 9시간 넘게</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>보완 · 수면</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>최근 3일, 잠든 시간과 일어난 시간이 얼마나 비슷했나요?</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>대체로 비슷했어요 / 1~2시간쯤 달랐어요 / 2시간 이상 달랐어요</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>거의 같음 / 1~2시간 / 2시간 이상</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>보완 · 수면</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>최근 7일, 하루에 잠은 대체로 몇 시간 잤나요?</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>7시간보다 적었어요 / 7~9시간 정도였어요 / 9시간보다 길었어요</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>7시간 미만 / 7~9시간 / 9시간 넘게</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>보완 · 수면</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>최근 7일, 잠잔 시간은 날마다 얼마나 달랐나요?</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>대체로 비슷했어요 / 1~2시간쯤 달랐어요 / 2시간 이상 달랐어요</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>거의 같음 / 1~2시간 / 2시간 이상</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>보완 · 피로감</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>오늘은 피로감이 어느 정도인가요?</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>전혀 피곤하지 않아요 / 조금 피곤해요 / 많이 피곤해요</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>피곤하지 않음 / 조금 피곤함 / 많이 피곤함</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>식사 시각 · 점심 (오후 2시 뒤)</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>점심은 언제쯤 드셨어요?</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>오후 1:00 이후 / 12:00~1:00 / 12:00 이전</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>점심은 언제쯤 드셨어요? (그대로)</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>1시 이후 / 12시~1시 사이 / 12시 이전</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>식사 시각 · 점심 (낮 12시대)</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>점심은 언제쯤 드셨어요?</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>오후 12:00 이후 / 오전~오후 11:00~12:00 / 오전 11:00 이전</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>점심은 언제쯤 드셨어요? (그대로)</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>12시 이후 / 11시~12시 사이 / 11시 이전</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
+++ b/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="바뀐 내용" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,29 +12,56 @@
     <sheet name="활동·수면 목표 문구" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
-    <font/>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFD92D20"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <b val="1"/>
       <color rgb="00D92D20"/>
@@ -50,7 +76,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2FF"/>
+        <fgColor rgb="FFEEF2FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,23 +90,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D5DE"/>
+        <color rgb="FFD0D5DE"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D5DE"/>
+        <color rgb="FFD0D5DE"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D5DE"/>
+        <color rgb="FFD0D5DE"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D5DE"/>
+        <color rgb="FFD0D5DE"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -106,9 +133,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -471,19 +501,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="6" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>바뀐 내용 · 기존 문구 → 바꾼 문구</t>
@@ -497,6 +526,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -534,7 +564,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>1</v>
       </c>
@@ -569,7 +599,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>2</v>
       </c>
@@ -604,7 +634,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>3</v>
       </c>
@@ -639,7 +669,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="3" t="n">
         <v>4</v>
       </c>
@@ -674,7 +704,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>5</v>
       </c>
@@ -709,7 +739,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>6</v>
       </c>
@@ -744,7 +774,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>7</v>
       </c>
@@ -770,7 +800,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>절반 미만 / 절반~평소 / 평소 이상</t>
+          <t>절반 미만 / 절반~평소 사이 / 그 이상</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -779,7 +809,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="34" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>8</v>
       </c>
@@ -808,9 +838,9 @@
           <t>7시간 미만 / 7~9시간 / 9시간 넘게</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
+      <c r="G12" s="3" t="n"/>
+    </row>
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>9</v>
       </c>
@@ -839,9 +869,9 @@
           <t>거의 같음 / 1~2시간 / 2시간 이상</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
+      <c r="G13" s="3" t="n"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>10</v>
       </c>
@@ -870,9 +900,9 @@
           <t>7시간 미만 / 7~9시간 / 9시간 넘게</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
+      <c r="G14" s="3" t="n"/>
+    </row>
+    <row r="15" ht="34" customHeight="1">
       <c r="A15" s="3" t="n">
         <v>11</v>
       </c>
@@ -901,9 +931,9 @@
           <t>거의 같음 / 1~2시간 / 2시간 이상</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
+      <c r="G15" s="3" t="n"/>
+    </row>
+    <row r="16" ht="34" customHeight="1">
       <c r="A16" s="3" t="n">
         <v>12</v>
       </c>
@@ -932,9 +962,9 @@
           <t>피곤하지 않음 / 조금 피곤함 / 많이 피곤함</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
+      <c r="G16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="34" customHeight="1">
       <c r="A17" s="3" t="n">
         <v>13</v>
       </c>
@@ -953,9 +983,9 @@
           <t>오후 1:00 이후 / 12:00~1:00 / 12:00 이전</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>점심은 언제쯤 드셨어요? (그대로)</t>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>점심은 언제쯤 드셨어요?</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -963,9 +993,9 @@
           <t>1시 이후 / 12시~1시 사이 / 12시 이전</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
+      <c r="G17" s="3" t="n"/>
+    </row>
+    <row r="18" ht="34" customHeight="1">
       <c r="A18" s="3" t="n">
         <v>14</v>
       </c>
@@ -984,9 +1014,9 @@
           <t>오후 12:00 이후 / 오전~오후 11:00~12:00 / 오전 11:00 이전</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>점심은 언제쯤 드셨어요? (그대로)</t>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>점심은 언제쯤 드셨어요?</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -994,11 +1024,11 @@
           <t>12시 이후 / 11시~12시 사이 / 11시 이전</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19"/>
+      <c r="G18" s="3" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -1009,22 +1039,21 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="6" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>오늘의 질문 · 질문과 선택지 (최종)</t>
@@ -1038,6 +1067,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1134,7 +1164,7 @@
           <t>진료정보에 확인 안 된 질환이 있는 날, 첫 질문</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="n"/>
       <c r="J5" s="5" t="n">
         <v>24</v>
       </c>
@@ -1142,7 +1172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>2</v>
       </c>
@@ -1181,7 +1211,7 @@
           <t>매일. 질환 확인 질문이 없는 날, 또는 그 답이 「아니요 · 모르겠어요」인 날</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="n"/>
       <c r="J6" s="5" t="n">
         <v>17</v>
       </c>
@@ -1228,7 +1258,7 @@
           <t>자정~오전 10시</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="n"/>
       <c r="J7" s="5" t="n">
         <v>17</v>
       </c>
@@ -1275,7 +1305,7 @@
           <t>오전 10~12시</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="n"/>
       <c r="J8" s="5" t="n">
         <v>14</v>
       </c>
@@ -1322,7 +1352,7 @@
           <t>낮 12시~오후 2시</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="n"/>
       <c r="J9" s="5" t="n">
         <v>13</v>
       </c>
@@ -1369,7 +1399,7 @@
           <t>오후 2~5시</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="n"/>
       <c r="J10" s="5" t="n">
         <v>13</v>
       </c>
@@ -1416,7 +1446,7 @@
           <t>오후 5~9시</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="n"/>
       <c r="J11" s="5" t="n">
         <v>13</v>
       </c>
@@ -1463,7 +1493,7 @@
           <t>오후 9시~자정</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="n"/>
       <c r="J12" s="5" t="n">
         <v>14</v>
       </c>
@@ -1510,7 +1540,7 @@
           <t>모든 끼니</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="n"/>
       <c r="J13" s="5" t="n">
         <v>23</v>
       </c>
@@ -1557,7 +1587,7 @@
           <t>모든 끼니</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="n"/>
       <c r="J14" s="5" t="n">
         <v>26</v>
       </c>
@@ -1604,7 +1634,7 @@
           <t>모든 끼니. 국물이 없던 끼니도 「먹지 않음」</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="n"/>
       <c r="J15" s="5" t="n">
         <v>20</v>
       </c>
@@ -1651,7 +1681,7 @@
           <t>오전 4~10시에 들어온 날만</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="n"/>
       <c r="J16" s="5" t="n">
         <v>17</v>
       </c>
@@ -1698,7 +1728,7 @@
           <t>모든 끼니</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="n"/>
       <c r="J17" s="5" t="n">
         <v>18</v>
       </c>
@@ -1745,7 +1775,7 @@
           <t>모든 끼니</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="n"/>
       <c r="J18" s="5" t="n">
         <v>30</v>
       </c>
@@ -1792,7 +1822,7 @@
           <t>모든 끼니</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="n"/>
       <c r="J19" s="5" t="n">
         <v>19</v>
       </c>
@@ -1800,7 +1830,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="34" customHeight="1">
       <c r="A20" s="3" t="n">
         <v>16</v>
       </c>
@@ -1851,7 +1881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="34" customHeight="1">
       <c r="A21" s="3" t="n">
         <v>17</v>
       </c>
@@ -1902,7 +1932,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="34" customHeight="1">
       <c r="A22" s="3" t="n">
         <v>18</v>
       </c>
@@ -1953,7 +1983,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="34" customHeight="1">
       <c r="A23" s="3" t="n">
         <v>19</v>
       </c>
@@ -2004,7 +2034,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="34" customHeight="1">
       <c r="A24" s="3" t="n">
         <v>20</v>
       </c>
@@ -2055,7 +2085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="34" customHeight="1">
       <c r="A25" s="3" t="n">
         <v>21</v>
       </c>
@@ -2106,7 +2136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="34" customHeight="1">
       <c r="A26" s="3" t="n">
         <v>22</v>
       </c>
@@ -2130,14 +2160,14 @@
           <t>절반 미만</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>절반~평소</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>평소 이상</t>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>절반~평소 사이</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>그 이상</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -2154,7 +2184,7 @@
         <v>36</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -2196,7 +2226,7 @@
           <t>하루 1개. 매일 물을 수 있음</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="n"/>
       <c r="J27" s="5" t="n">
         <v>21</v>
       </c>
@@ -2243,7 +2273,7 @@
           <t>3일 뒤에 다시 물음 · 7일에 2번까지</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="n"/>
       <c r="J28" s="5" t="n">
         <v>32</v>
       </c>
@@ -2251,7 +2281,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="34" customHeight="1">
       <c r="A29" s="3" t="n">
         <v>25</v>
       </c>
@@ -2290,7 +2320,7 @@
           <t>하루 1개 · 7일에 2개까지. 위에서부터 먼저 물음. 같은 질문은 7일 뒤에 다시 물음</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="n"/>
       <c r="J29" s="5" t="n">
         <v>27</v>
       </c>
@@ -2298,7 +2328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="34" customHeight="1">
       <c r="A30" s="3" t="n">
         <v>26</v>
       </c>
@@ -2337,7 +2367,7 @@
           <t>하루 1개 · 7일에 2개까지. 위에서부터 먼저 물음. 같은 질문은 7일 뒤에 다시 물음</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="n"/>
       <c r="J30" s="5" t="n">
         <v>27</v>
       </c>
@@ -2384,7 +2414,7 @@
           <t>하루 1개 · 7일에 4번까지</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="n"/>
       <c r="J31" s="5" t="n">
         <v>18</v>
       </c>
@@ -2392,6 +2422,7 @@
         <v>7</v>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -2425,19 +2456,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H407"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="6" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>식이 목표 문구 (사용 403개)</t>
@@ -2451,6 +2481,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -2493,7 +2524,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>1</v>
       </c>
@@ -2573,7 +2604,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>3</v>
       </c>
@@ -2613,7 +2644,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="3" t="n">
         <v>4</v>
       </c>
@@ -2653,7 +2684,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>5</v>
       </c>
@@ -2693,7 +2724,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>6</v>
       </c>
@@ -2733,7 +2764,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="34" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>7</v>
       </c>
@@ -2773,7 +2804,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="34" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>8</v>
       </c>
@@ -2853,7 +2884,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="34" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>10</v>
       </c>
@@ -2893,7 +2924,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="34" customHeight="1">
       <c r="A15" s="3" t="n">
         <v>11</v>
       </c>
@@ -2933,7 +2964,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="34" customHeight="1">
       <c r="A16" s="3" t="n">
         <v>12</v>
       </c>
@@ -2973,7 +3004,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="34" customHeight="1">
       <c r="A17" s="3" t="n">
         <v>13</v>
       </c>
@@ -3013,7 +3044,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="34" customHeight="1">
       <c r="A18" s="3" t="n">
         <v>14</v>
       </c>
@@ -3053,7 +3084,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="34" customHeight="1">
       <c r="A19" s="3" t="n">
         <v>15</v>
       </c>
@@ -3093,7 +3124,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="34" customHeight="1">
       <c r="A20" s="3" t="n">
         <v>16</v>
       </c>
@@ -3133,7 +3164,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="34" customHeight="1">
       <c r="A21" s="3" t="n">
         <v>17</v>
       </c>
@@ -3173,7 +3204,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="34" customHeight="1">
       <c r="A22" s="3" t="n">
         <v>18</v>
       </c>
@@ -3213,7 +3244,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="34" customHeight="1">
       <c r="A23" s="3" t="n">
         <v>19</v>
       </c>
@@ -3253,7 +3284,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="34" customHeight="1">
       <c r="A24" s="3" t="n">
         <v>20</v>
       </c>
@@ -3293,7 +3324,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="34" customHeight="1">
       <c r="A25" s="3" t="n">
         <v>21</v>
       </c>
@@ -3333,7 +3364,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="34" customHeight="1">
       <c r="A26" s="3" t="n">
         <v>22</v>
       </c>
@@ -3413,7 +3444,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="34" customHeight="1">
       <c r="A28" s="3" t="n">
         <v>24</v>
       </c>
@@ -3453,7 +3484,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="34" customHeight="1">
       <c r="A29" s="3" t="n">
         <v>25</v>
       </c>
@@ -3493,7 +3524,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="34" customHeight="1">
       <c r="A30" s="3" t="n">
         <v>26</v>
       </c>
@@ -3502,7 +3533,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -3529,7 +3560,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="34" customHeight="1">
       <c r="A31" s="3" t="n">
         <v>27</v>
       </c>
@@ -3538,7 +3569,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -3565,7 +3596,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="34" customHeight="1">
       <c r="A32" s="3" t="n">
         <v>28</v>
       </c>
@@ -3574,7 +3605,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -3601,7 +3632,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="34" customHeight="1">
       <c r="A33" s="3" t="n">
         <v>29</v>
       </c>
@@ -3610,7 +3641,7 @@
           <t>부담 줄이기 풀</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -3637,7 +3668,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="34" customHeight="1">
       <c r="A34" s="3" t="n">
         <v>30</v>
       </c>
@@ -3646,7 +3677,7 @@
           <t>부담 줄이기 풀</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
+      <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -3673,7 +3704,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="34" customHeight="1">
       <c r="A35" s="3" t="n">
         <v>31</v>
       </c>
@@ -3682,7 +3713,7 @@
           <t>부담 줄이기 풀</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -3749,7 +3780,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="34" customHeight="1">
       <c r="A37" s="3" t="n">
         <v>33</v>
       </c>
@@ -3789,7 +3820,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="34" customHeight="1">
       <c r="A38" s="3" t="n">
         <v>34</v>
       </c>
@@ -3829,7 +3860,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="34" customHeight="1">
       <c r="A39" s="3" t="n">
         <v>35</v>
       </c>
@@ -3869,7 +3900,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="34" customHeight="1">
       <c r="A40" s="3" t="n">
         <v>36</v>
       </c>
@@ -3909,7 +3940,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="34" customHeight="1">
       <c r="A41" s="3" t="n">
         <v>37</v>
       </c>
@@ -3949,7 +3980,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="34" customHeight="1">
       <c r="A42" s="3" t="n">
         <v>38</v>
       </c>
@@ -4029,7 +4060,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="34" customHeight="1">
       <c r="A44" s="3" t="n">
         <v>40</v>
       </c>
@@ -4069,7 +4100,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="34" customHeight="1">
       <c r="A45" s="3" t="n">
         <v>41</v>
       </c>
@@ -4109,7 +4140,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="34" customHeight="1">
       <c r="A46" s="3" t="n">
         <v>42</v>
       </c>
@@ -4149,7 +4180,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="34" customHeight="1">
       <c r="A47" s="3" t="n">
         <v>43</v>
       </c>
@@ -4189,7 +4220,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="34" customHeight="1">
       <c r="A48" s="3" t="n">
         <v>44</v>
       </c>
@@ -4229,7 +4260,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="34" customHeight="1">
       <c r="A49" s="3" t="n">
         <v>45</v>
       </c>
@@ -4309,7 +4340,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="34" customHeight="1">
       <c r="A51" s="3" t="n">
         <v>47</v>
       </c>
@@ -4349,7 +4380,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="34" customHeight="1">
       <c r="A52" s="3" t="n">
         <v>48</v>
       </c>
@@ -4389,7 +4420,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="34" customHeight="1">
       <c r="A53" s="3" t="n">
         <v>49</v>
       </c>
@@ -4429,7 +4460,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="34" customHeight="1">
       <c r="A54" s="3" t="n">
         <v>50</v>
       </c>
@@ -4669,7 +4700,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="34" customHeight="1">
       <c r="A60" s="3" t="n">
         <v>56</v>
       </c>
@@ -4709,7 +4740,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="34" customHeight="1">
       <c r="A61" s="3" t="n">
         <v>57</v>
       </c>
@@ -4789,7 +4820,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="34" customHeight="1">
       <c r="A63" s="3" t="n">
         <v>59</v>
       </c>
@@ -4829,7 +4860,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="34" customHeight="1">
       <c r="A64" s="3" t="n">
         <v>60</v>
       </c>
@@ -4869,7 +4900,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="34" customHeight="1">
       <c r="A65" s="3" t="n">
         <v>61</v>
       </c>
@@ -4878,7 +4909,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr"/>
+      <c r="C65" s="3" t="n"/>
       <c r="D65" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -4905,7 +4936,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="34" customHeight="1">
       <c r="A66" s="3" t="n">
         <v>62</v>
       </c>
@@ -4914,7 +4945,7 @@
           <t>부담 줄이기 풀</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr"/>
+      <c r="C66" s="3" t="n"/>
       <c r="D66" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -4981,7 +5012,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="34" customHeight="1">
       <c r="A68" s="3" t="n">
         <v>64</v>
       </c>
@@ -5061,7 +5092,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="34" customHeight="1">
       <c r="A70" s="3" t="n">
         <v>66</v>
       </c>
@@ -5101,7 +5132,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="34" customHeight="1">
       <c r="A71" s="3" t="n">
         <v>67</v>
       </c>
@@ -5181,7 +5212,7 @@
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="34" customHeight="1">
       <c r="A73" s="3" t="n">
         <v>69</v>
       </c>
@@ -5221,7 +5252,7 @@
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="34" customHeight="1">
       <c r="A74" s="3" t="n">
         <v>70</v>
       </c>
@@ -5301,7 +5332,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="34" customHeight="1">
       <c r="A76" s="3" t="n">
         <v>72</v>
       </c>
@@ -5381,7 +5412,7 @@
         </is>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="34" customHeight="1">
       <c r="A78" s="3" t="n">
         <v>74</v>
       </c>
@@ -5501,7 +5532,7 @@
         </is>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="34" customHeight="1">
       <c r="A81" s="3" t="n">
         <v>77</v>
       </c>
@@ -5541,7 +5572,7 @@
         </is>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="34" customHeight="1">
       <c r="A82" s="3" t="n">
         <v>78</v>
       </c>
@@ -5621,7 +5652,7 @@
         </is>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="34" customHeight="1">
       <c r="A84" s="3" t="n">
         <v>80</v>
       </c>
@@ -5661,7 +5692,7 @@
         </is>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="34" customHeight="1">
       <c r="A85" s="3" t="n">
         <v>81</v>
       </c>
@@ -5701,7 +5732,7 @@
         </is>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="34" customHeight="1">
       <c r="A86" s="3" t="n">
         <v>82</v>
       </c>
@@ -5741,7 +5772,7 @@
         </is>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="34" customHeight="1">
       <c r="A87" s="3" t="n">
         <v>83</v>
       </c>
@@ -5781,7 +5812,7 @@
         </is>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="34" customHeight="1">
       <c r="A88" s="3" t="n">
         <v>84</v>
       </c>
@@ -5941,7 +5972,7 @@
         </is>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="34" customHeight="1">
       <c r="A92" s="3" t="n">
         <v>88</v>
       </c>
@@ -5981,7 +6012,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="34" customHeight="1">
       <c r="A93" s="3" t="n">
         <v>89</v>
       </c>
@@ -6101,7 +6132,7 @@
         </is>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="34" customHeight="1">
       <c r="A96" s="3" t="n">
         <v>92</v>
       </c>
@@ -6141,7 +6172,7 @@
         </is>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="34" customHeight="1">
       <c r="A97" s="3" t="n">
         <v>93</v>
       </c>
@@ -6221,7 +6252,7 @@
         </is>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="34" customHeight="1">
       <c r="A99" s="3" t="n">
         <v>95</v>
       </c>
@@ -6301,7 +6332,7 @@
         </is>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="34" customHeight="1">
       <c r="A101" s="3" t="n">
         <v>97</v>
       </c>
@@ -6381,7 +6412,7 @@
         </is>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="34" customHeight="1">
       <c r="A103" s="3" t="n">
         <v>99</v>
       </c>
@@ -6421,7 +6452,7 @@
         </is>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="34" customHeight="1">
       <c r="A104" s="3" t="n">
         <v>100</v>
       </c>
@@ -6501,7 +6532,7 @@
         </is>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="34" customHeight="1">
       <c r="A106" s="3" t="n">
         <v>102</v>
       </c>
@@ -6510,7 +6541,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr"/>
+      <c r="C106" s="3" t="n"/>
       <c r="D106" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -6537,7 +6568,7 @@
         </is>
       </c>
     </row>
-    <row r="107">
+    <row r="107" ht="34" customHeight="1">
       <c r="A107" s="3" t="n">
         <v>103</v>
       </c>
@@ -6546,7 +6577,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr"/>
+      <c r="C107" s="3" t="n"/>
       <c r="D107" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -6573,7 +6604,7 @@
         </is>
       </c>
     </row>
-    <row r="108">
+    <row r="108" ht="34" customHeight="1">
       <c r="A108" s="3" t="n">
         <v>104</v>
       </c>
@@ -6582,7 +6613,7 @@
           <t>부담 줄이기 풀</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr"/>
+      <c r="C108" s="3" t="n"/>
       <c r="D108" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -6609,7 +6640,7 @@
         </is>
       </c>
     </row>
-    <row r="109">
+    <row r="109" ht="34" customHeight="1">
       <c r="A109" s="3" t="n">
         <v>105</v>
       </c>
@@ -6618,7 +6649,7 @@
           <t>부담 줄이기 풀</t>
         </is>
       </c>
-      <c r="C109" s="3" t="inlineStr"/>
+      <c r="C109" s="3" t="n"/>
       <c r="D109" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -6685,7 +6716,7 @@
         </is>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="34" customHeight="1">
       <c r="A111" s="3" t="n">
         <v>107</v>
       </c>
@@ -6725,7 +6756,7 @@
         </is>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="34" customHeight="1">
       <c r="A112" s="3" t="n">
         <v>108</v>
       </c>
@@ -6765,7 +6796,7 @@
         </is>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="34" customHeight="1">
       <c r="A113" s="3" t="n">
         <v>109</v>
       </c>
@@ -6845,7 +6876,7 @@
         </is>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="34" customHeight="1">
       <c r="A115" s="3" t="n">
         <v>111</v>
       </c>
@@ -6885,7 +6916,7 @@
         </is>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="34" customHeight="1">
       <c r="A116" s="3" t="n">
         <v>112</v>
       </c>
@@ -6965,7 +6996,7 @@
         </is>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="34" customHeight="1">
       <c r="A118" s="3" t="n">
         <v>114</v>
       </c>
@@ -7165,7 +7196,7 @@
         </is>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="34" customHeight="1">
       <c r="A123" s="3" t="n">
         <v>119</v>
       </c>
@@ -7245,7 +7276,7 @@
         </is>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="34" customHeight="1">
       <c r="A125" s="3" t="n">
         <v>121</v>
       </c>
@@ -7325,7 +7356,7 @@
         </is>
       </c>
     </row>
-    <row r="127">
+    <row r="127" ht="34" customHeight="1">
       <c r="A127" s="3" t="n">
         <v>123</v>
       </c>
@@ -7485,7 +7516,7 @@
         </is>
       </c>
     </row>
-    <row r="131">
+    <row r="131" ht="34" customHeight="1">
       <c r="A131" s="3" t="n">
         <v>127</v>
       </c>
@@ -7494,7 +7525,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr"/>
+      <c r="C131" s="3" t="n"/>
       <c r="D131" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -7521,7 +7552,7 @@
         </is>
       </c>
     </row>
-    <row r="132">
+    <row r="132" ht="34" customHeight="1">
       <c r="A132" s="3" t="n">
         <v>128</v>
       </c>
@@ -7530,7 +7561,7 @@
           <t>부담 줄이기 풀</t>
         </is>
       </c>
-      <c r="C132" s="3" t="inlineStr"/>
+      <c r="C132" s="3" t="n"/>
       <c r="D132" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -7557,7 +7588,7 @@
         </is>
       </c>
     </row>
-    <row r="133">
+    <row r="133" ht="34" customHeight="1">
       <c r="A133" s="3" t="n">
         <v>129</v>
       </c>
@@ -7566,7 +7597,7 @@
           <t>부담 줄이기 풀</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr"/>
+      <c r="C133" s="3" t="n"/>
       <c r="D133" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -7593,7 +7624,7 @@
         </is>
       </c>
     </row>
-    <row r="134">
+    <row r="134" ht="34" customHeight="1">
       <c r="A134" s="3" t="n">
         <v>130</v>
       </c>
@@ -7633,7 +7664,7 @@
         </is>
       </c>
     </row>
-    <row r="135">
+    <row r="135" ht="34" customHeight="1">
       <c r="A135" s="3" t="n">
         <v>131</v>
       </c>
@@ -7673,7 +7704,7 @@
         </is>
       </c>
     </row>
-    <row r="136">
+    <row r="136" ht="34" customHeight="1">
       <c r="A136" s="3" t="n">
         <v>132</v>
       </c>
@@ -7713,7 +7744,7 @@
         </is>
       </c>
     </row>
-    <row r="137">
+    <row r="137" ht="34" customHeight="1">
       <c r="A137" s="3" t="n">
         <v>133</v>
       </c>
@@ -7793,7 +7824,7 @@
         </is>
       </c>
     </row>
-    <row r="139">
+    <row r="139" ht="34" customHeight="1">
       <c r="A139" s="3" t="n">
         <v>135</v>
       </c>
@@ -7873,7 +7904,7 @@
         </is>
       </c>
     </row>
-    <row r="141">
+    <row r="141" ht="34" customHeight="1">
       <c r="A141" s="3" t="n">
         <v>137</v>
       </c>
@@ -7953,7 +7984,7 @@
         </is>
       </c>
     </row>
-    <row r="143">
+    <row r="143" ht="34" customHeight="1">
       <c r="A143" s="3" t="n">
         <v>139</v>
       </c>
@@ -7993,7 +8024,7 @@
         </is>
       </c>
     </row>
-    <row r="144">
+    <row r="144" ht="34" customHeight="1">
       <c r="A144" s="3" t="n">
         <v>140</v>
       </c>
@@ -8073,7 +8104,7 @@
         </is>
       </c>
     </row>
-    <row r="146">
+    <row r="146" ht="34" customHeight="1">
       <c r="A146" s="3" t="n">
         <v>142</v>
       </c>
@@ -8082,7 +8113,7 @@
           <t>부담 줄이기 풀</t>
         </is>
       </c>
-      <c r="C146" s="3" t="inlineStr"/>
+      <c r="C146" s="3" t="n"/>
       <c r="D146" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -8109,7 +8140,7 @@
         </is>
       </c>
     </row>
-    <row r="147">
+    <row r="147" ht="34" customHeight="1">
       <c r="A147" s="3" t="n">
         <v>143</v>
       </c>
@@ -8189,7 +8220,7 @@
         </is>
       </c>
     </row>
-    <row r="149">
+    <row r="149" ht="34" customHeight="1">
       <c r="A149" s="3" t="n">
         <v>145</v>
       </c>
@@ -8229,7 +8260,7 @@
         </is>
       </c>
     </row>
-    <row r="150">
+    <row r="150" ht="34" customHeight="1">
       <c r="A150" s="3" t="n">
         <v>146</v>
       </c>
@@ -8269,7 +8300,7 @@
         </is>
       </c>
     </row>
-    <row r="151">
+    <row r="151" ht="34" customHeight="1">
       <c r="A151" s="3" t="n">
         <v>147</v>
       </c>
@@ -8309,7 +8340,7 @@
         </is>
       </c>
     </row>
-    <row r="152">
+    <row r="152" ht="34" customHeight="1">
       <c r="A152" s="3" t="n">
         <v>148</v>
       </c>
@@ -8349,7 +8380,7 @@
         </is>
       </c>
     </row>
-    <row r="153">
+    <row r="153" ht="34" customHeight="1">
       <c r="A153" s="3" t="n">
         <v>149</v>
       </c>
@@ -8429,7 +8460,7 @@
         </is>
       </c>
     </row>
-    <row r="155">
+    <row r="155" ht="34" customHeight="1">
       <c r="A155" s="3" t="n">
         <v>151</v>
       </c>
@@ -8469,7 +8500,7 @@
         </is>
       </c>
     </row>
-    <row r="156">
+    <row r="156" ht="34" customHeight="1">
       <c r="A156" s="3" t="n">
         <v>152</v>
       </c>
@@ -8549,7 +8580,7 @@
         </is>
       </c>
     </row>
-    <row r="158">
+    <row r="158" ht="34" customHeight="1">
       <c r="A158" s="3" t="n">
         <v>154</v>
       </c>
@@ -8789,7 +8820,7 @@
         </is>
       </c>
     </row>
-    <row r="164">
+    <row r="164" ht="34" customHeight="1">
       <c r="A164" s="3" t="n">
         <v>160</v>
       </c>
@@ -8989,7 +9020,7 @@
         </is>
       </c>
     </row>
-    <row r="169">
+    <row r="169" ht="34" customHeight="1">
       <c r="A169" s="3" t="n">
         <v>165</v>
       </c>
@@ -9038,7 +9069,7 @@
           <t>축 × 단계</t>
         </is>
       </c>
-      <c r="C170" s="3" t="inlineStr"/>
+      <c r="C170" s="3" t="n"/>
       <c r="D170" s="3" t="inlineStr">
         <is>
           <t>기본</t>
@@ -9065,7 +9096,7 @@
         </is>
       </c>
     </row>
-    <row r="171">
+    <row r="171" ht="34" customHeight="1">
       <c r="A171" s="3" t="n">
         <v>167</v>
       </c>
@@ -9105,7 +9136,7 @@
         </is>
       </c>
     </row>
-    <row r="172">
+    <row r="172" ht="34" customHeight="1">
       <c r="A172" s="3" t="n">
         <v>168</v>
       </c>
@@ -9145,7 +9176,7 @@
         </is>
       </c>
     </row>
-    <row r="173">
+    <row r="173" ht="34" customHeight="1">
       <c r="A173" s="3" t="n">
         <v>169</v>
       </c>
@@ -9185,7 +9216,7 @@
         </is>
       </c>
     </row>
-    <row r="174">
+    <row r="174" ht="34" customHeight="1">
       <c r="A174" s="3" t="n">
         <v>170</v>
       </c>
@@ -9265,7 +9296,7 @@
         </is>
       </c>
     </row>
-    <row r="176">
+    <row r="176" ht="34" customHeight="1">
       <c r="A176" s="3" t="n">
         <v>172</v>
       </c>
@@ -9274,7 +9305,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C176" s="3" t="inlineStr"/>
+      <c r="C176" s="3" t="n"/>
       <c r="D176" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -9301,7 +9332,7 @@
         </is>
       </c>
     </row>
-    <row r="177">
+    <row r="177" ht="34" customHeight="1">
       <c r="A177" s="3" t="n">
         <v>173</v>
       </c>
@@ -9310,7 +9341,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C177" s="3" t="inlineStr"/>
+      <c r="C177" s="3" t="n"/>
       <c r="D177" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -9337,7 +9368,7 @@
         </is>
       </c>
     </row>
-    <row r="178">
+    <row r="178" ht="34" customHeight="1">
       <c r="A178" s="3" t="n">
         <v>174</v>
       </c>
@@ -9346,7 +9377,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C178" s="3" t="inlineStr"/>
+      <c r="C178" s="3" t="n"/>
       <c r="D178" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -9373,7 +9404,7 @@
         </is>
       </c>
     </row>
-    <row r="179">
+    <row r="179" ht="34" customHeight="1">
       <c r="A179" s="3" t="n">
         <v>175</v>
       </c>
@@ -9382,7 +9413,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C179" s="3" t="inlineStr"/>
+      <c r="C179" s="3" t="n"/>
       <c r="D179" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -9409,7 +9440,7 @@
         </is>
       </c>
     </row>
-    <row r="180">
+    <row r="180" ht="34" customHeight="1">
       <c r="A180" s="3" t="n">
         <v>176</v>
       </c>
@@ -9418,7 +9449,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C180" s="3" t="inlineStr"/>
+      <c r="C180" s="3" t="n"/>
       <c r="D180" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -9445,7 +9476,7 @@
         </is>
       </c>
     </row>
-    <row r="181">
+    <row r="181" ht="34" customHeight="1">
       <c r="A181" s="3" t="n">
         <v>177</v>
       </c>
@@ -9525,7 +9556,7 @@
         </is>
       </c>
     </row>
-    <row r="183">
+    <row r="183" ht="34" customHeight="1">
       <c r="A183" s="3" t="n">
         <v>179</v>
       </c>
@@ -9605,7 +9636,7 @@
         </is>
       </c>
     </row>
-    <row r="185">
+    <row r="185" ht="34" customHeight="1">
       <c r="A185" s="3" t="n">
         <v>181</v>
       </c>
@@ -9645,7 +9676,7 @@
         </is>
       </c>
     </row>
-    <row r="186">
+    <row r="186" ht="34" customHeight="1">
       <c r="A186" s="3" t="n">
         <v>182</v>
       </c>
@@ -9845,7 +9876,7 @@
         </is>
       </c>
     </row>
-    <row r="191">
+    <row r="191" ht="34" customHeight="1">
       <c r="A191" s="3" t="n">
         <v>187</v>
       </c>
@@ -10045,7 +10076,7 @@
         </is>
       </c>
     </row>
-    <row r="196">
+    <row r="196" ht="34" customHeight="1">
       <c r="A196" s="3" t="n">
         <v>192</v>
       </c>
@@ -10125,7 +10156,7 @@
         </is>
       </c>
     </row>
-    <row r="198">
+    <row r="198" ht="34" customHeight="1">
       <c r="A198" s="3" t="n">
         <v>194</v>
       </c>
@@ -10134,7 +10165,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C198" s="3" t="inlineStr"/>
+      <c r="C198" s="3" t="n"/>
       <c r="D198" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -10161,7 +10192,7 @@
         </is>
       </c>
     </row>
-    <row r="199">
+    <row r="199" ht="34" customHeight="1">
       <c r="A199" s="3" t="n">
         <v>195</v>
       </c>
@@ -10170,7 +10201,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C199" s="3" t="inlineStr"/>
+      <c r="C199" s="3" t="n"/>
       <c r="D199" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -10197,7 +10228,7 @@
         </is>
       </c>
     </row>
-    <row r="200">
+    <row r="200" ht="34" customHeight="1">
       <c r="A200" s="3" t="n">
         <v>196</v>
       </c>
@@ -10206,7 +10237,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C200" s="3" t="inlineStr"/>
+      <c r="C200" s="3" t="n"/>
       <c r="D200" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -10233,7 +10264,7 @@
         </is>
       </c>
     </row>
-    <row r="201">
+    <row r="201" ht="34" customHeight="1">
       <c r="A201" s="3" t="n">
         <v>197</v>
       </c>
@@ -10273,7 +10304,7 @@
         </is>
       </c>
     </row>
-    <row r="202">
+    <row r="202" ht="34" customHeight="1">
       <c r="A202" s="3" t="n">
         <v>198</v>
       </c>
@@ -10313,7 +10344,7 @@
         </is>
       </c>
     </row>
-    <row r="203">
+    <row r="203" ht="34" customHeight="1">
       <c r="A203" s="3" t="n">
         <v>199</v>
       </c>
@@ -10473,7 +10504,7 @@
         </is>
       </c>
     </row>
-    <row r="207">
+    <row r="207" ht="34" customHeight="1">
       <c r="A207" s="3" t="n">
         <v>203</v>
       </c>
@@ -10513,7 +10544,7 @@
         </is>
       </c>
     </row>
-    <row r="208">
+    <row r="208" ht="34" customHeight="1">
       <c r="A208" s="3" t="n">
         <v>204</v>
       </c>
@@ -10633,7 +10664,7 @@
         </is>
       </c>
     </row>
-    <row r="211">
+    <row r="211" ht="34" customHeight="1">
       <c r="A211" s="3" t="n">
         <v>207</v>
       </c>
@@ -10673,7 +10704,7 @@
         </is>
       </c>
     </row>
-    <row r="212">
+    <row r="212" ht="34" customHeight="1">
       <c r="A212" s="3" t="n">
         <v>208</v>
       </c>
@@ -10753,7 +10784,7 @@
         </is>
       </c>
     </row>
-    <row r="214">
+    <row r="214" ht="34" customHeight="1">
       <c r="A214" s="3" t="n">
         <v>210</v>
       </c>
@@ -10833,7 +10864,7 @@
         </is>
       </c>
     </row>
-    <row r="216">
+    <row r="216" ht="34" customHeight="1">
       <c r="A216" s="3" t="n">
         <v>212</v>
       </c>
@@ -10873,7 +10904,7 @@
         </is>
       </c>
     </row>
-    <row r="217">
+    <row r="217" ht="34" customHeight="1">
       <c r="A217" s="3" t="n">
         <v>213</v>
       </c>
@@ -10882,7 +10913,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C217" s="3" t="inlineStr"/>
+      <c r="C217" s="3" t="n"/>
       <c r="D217" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -10909,7 +10940,7 @@
         </is>
       </c>
     </row>
-    <row r="218">
+    <row r="218" ht="34" customHeight="1">
       <c r="A218" s="3" t="n">
         <v>214</v>
       </c>
@@ -10918,7 +10949,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C218" s="3" t="inlineStr"/>
+      <c r="C218" s="3" t="n"/>
       <c r="D218" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -10945,7 +10976,7 @@
         </is>
       </c>
     </row>
-    <row r="219">
+    <row r="219" ht="34" customHeight="1">
       <c r="A219" s="3" t="n">
         <v>215</v>
       </c>
@@ -10985,7 +11016,7 @@
         </is>
       </c>
     </row>
-    <row r="220">
+    <row r="220" ht="34" customHeight="1">
       <c r="A220" s="3" t="n">
         <v>216</v>
       </c>
@@ -11025,7 +11056,7 @@
         </is>
       </c>
     </row>
-    <row r="221">
+    <row r="221" ht="34" customHeight="1">
       <c r="A221" s="3" t="n">
         <v>217</v>
       </c>
@@ -11225,7 +11256,7 @@
         </is>
       </c>
     </row>
-    <row r="226">
+    <row r="226" ht="34" customHeight="1">
       <c r="A226" s="3" t="n">
         <v>222</v>
       </c>
@@ -11345,7 +11376,7 @@
         </is>
       </c>
     </row>
-    <row r="229">
+    <row r="229" ht="34" customHeight="1">
       <c r="A229" s="3" t="n">
         <v>225</v>
       </c>
@@ -11385,7 +11416,7 @@
         </is>
       </c>
     </row>
-    <row r="230">
+    <row r="230" ht="34" customHeight="1">
       <c r="A230" s="3" t="n">
         <v>226</v>
       </c>
@@ -11585,7 +11616,7 @@
         </is>
       </c>
     </row>
-    <row r="235">
+    <row r="235" ht="34" customHeight="1">
       <c r="A235" s="3" t="n">
         <v>231</v>
       </c>
@@ -11625,7 +11656,7 @@
         </is>
       </c>
     </row>
-    <row r="236">
+    <row r="236" ht="34" customHeight="1">
       <c r="A236" s="3" t="n">
         <v>232</v>
       </c>
@@ -11745,7 +11776,7 @@
         </is>
       </c>
     </row>
-    <row r="239">
+    <row r="239" ht="34" customHeight="1">
       <c r="A239" s="3" t="n">
         <v>235</v>
       </c>
@@ -11865,7 +11896,7 @@
         </is>
       </c>
     </row>
-    <row r="242">
+    <row r="242" ht="34" customHeight="1">
       <c r="A242" s="3" t="n">
         <v>238</v>
       </c>
@@ -11874,7 +11905,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C242" s="3" t="inlineStr"/>
+      <c r="C242" s="3" t="n"/>
       <c r="D242" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -11901,7 +11932,7 @@
         </is>
       </c>
     </row>
-    <row r="243">
+    <row r="243" ht="34" customHeight="1">
       <c r="A243" s="3" t="n">
         <v>239</v>
       </c>
@@ -11910,7 +11941,7 @@
           <t>회복 풀</t>
         </is>
       </c>
-      <c r="C243" s="3" t="inlineStr"/>
+      <c r="C243" s="3" t="n"/>
       <c r="D243" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -11937,7 +11968,7 @@
         </is>
       </c>
     </row>
-    <row r="244">
+    <row r="244" ht="34" customHeight="1">
       <c r="A244" s="3" t="n">
         <v>240</v>
       </c>
@@ -12097,7 +12128,7 @@
         </is>
       </c>
     </row>
-    <row r="248">
+    <row r="248" ht="34" customHeight="1">
       <c r="A248" s="3" t="n">
         <v>244</v>
       </c>
@@ -12137,7 +12168,7 @@
         </is>
       </c>
     </row>
-    <row r="249">
+    <row r="249" ht="34" customHeight="1">
       <c r="A249" s="3" t="n">
         <v>245</v>
       </c>
@@ -12257,7 +12288,7 @@
         </is>
       </c>
     </row>
-    <row r="252">
+    <row r="252" ht="34" customHeight="1">
       <c r="A252" s="3" t="n">
         <v>248</v>
       </c>
@@ -12297,7 +12328,7 @@
         </is>
       </c>
     </row>
-    <row r="253">
+    <row r="253" ht="34" customHeight="1">
       <c r="A253" s="3" t="n">
         <v>249</v>
       </c>
@@ -12377,7 +12408,7 @@
         </is>
       </c>
     </row>
-    <row r="255">
+    <row r="255" ht="34" customHeight="1">
       <c r="A255" s="3" t="n">
         <v>251</v>
       </c>
@@ -12457,7 +12488,7 @@
         </is>
       </c>
     </row>
-    <row r="257">
+    <row r="257" ht="34" customHeight="1">
       <c r="A257" s="3" t="n">
         <v>253</v>
       </c>
@@ -12497,7 +12528,7 @@
         </is>
       </c>
     </row>
-    <row r="258">
+    <row r="258" ht="34" customHeight="1">
       <c r="A258" s="3" t="n">
         <v>254</v>
       </c>
@@ -12617,7 +12648,7 @@
         </is>
       </c>
     </row>
-    <row r="261">
+    <row r="261" ht="34" customHeight="1">
       <c r="A261" s="3" t="n">
         <v>257</v>
       </c>
@@ -12697,7 +12728,7 @@
         </is>
       </c>
     </row>
-    <row r="263">
+    <row r="263" ht="34" customHeight="1">
       <c r="A263" s="3" t="n">
         <v>259</v>
       </c>
@@ -12777,7 +12808,7 @@
         </is>
       </c>
     </row>
-    <row r="265">
+    <row r="265" ht="34" customHeight="1">
       <c r="A265" s="3" t="n">
         <v>261</v>
       </c>
@@ -12817,7 +12848,7 @@
         </is>
       </c>
     </row>
-    <row r="266">
+    <row r="266" ht="34" customHeight="1">
       <c r="A266" s="3" t="n">
         <v>262</v>
       </c>
@@ -12897,7 +12928,7 @@
         </is>
       </c>
     </row>
-    <row r="268">
+    <row r="268" ht="34" customHeight="1">
       <c r="A268" s="3" t="n">
         <v>264</v>
       </c>
@@ -13137,7 +13168,7 @@
         </is>
       </c>
     </row>
-    <row r="274">
+    <row r="274" ht="34" customHeight="1">
       <c r="A274" s="3" t="n">
         <v>270</v>
       </c>
@@ -13257,7 +13288,7 @@
         </is>
       </c>
     </row>
-    <row r="277">
+    <row r="277" ht="34" customHeight="1">
       <c r="A277" s="3" t="n">
         <v>273</v>
       </c>
@@ -13337,7 +13368,7 @@
         </is>
       </c>
     </row>
-    <row r="279">
+    <row r="279" ht="34" customHeight="1">
       <c r="A279" s="3" t="n">
         <v>275</v>
       </c>
@@ -13377,7 +13408,7 @@
         </is>
       </c>
     </row>
-    <row r="280">
+    <row r="280" ht="34" customHeight="1">
       <c r="A280" s="3" t="n">
         <v>276</v>
       </c>
@@ -13537,7 +13568,7 @@
         </is>
       </c>
     </row>
-    <row r="284">
+    <row r="284" ht="34" customHeight="1">
       <c r="A284" s="3" t="n">
         <v>280</v>
       </c>
@@ -13577,7 +13608,7 @@
         </is>
       </c>
     </row>
-    <row r="285">
+    <row r="285" ht="34" customHeight="1">
       <c r="A285" s="3" t="n">
         <v>281</v>
       </c>
@@ -14097,7 +14128,7 @@
         </is>
       </c>
     </row>
-    <row r="298">
+    <row r="298" ht="34" customHeight="1">
       <c r="A298" s="3" t="n">
         <v>294</v>
       </c>
@@ -14106,7 +14137,7 @@
           <t>부담 줄이기 풀</t>
         </is>
       </c>
-      <c r="C298" s="3" t="inlineStr"/>
+      <c r="C298" s="3" t="n"/>
       <c r="D298" s="3" t="inlineStr">
         <is>
           <t>단계 없음</t>
@@ -14133,7 +14164,7 @@
         </is>
       </c>
     </row>
-    <row r="299">
+    <row r="299" ht="34" customHeight="1">
       <c r="A299" s="3" t="n">
         <v>295</v>
       </c>
@@ -14373,7 +14404,7 @@
         </is>
       </c>
     </row>
-    <row r="305">
+    <row r="305" ht="34" customHeight="1">
       <c r="A305" s="3" t="n">
         <v>301</v>
       </c>
@@ -14733,7 +14764,7 @@
         </is>
       </c>
     </row>
-    <row r="314">
+    <row r="314" ht="34" customHeight="1">
       <c r="A314" s="3" t="n">
         <v>310</v>
       </c>
@@ -14773,7 +14804,7 @@
         </is>
       </c>
     </row>
-    <row r="315">
+    <row r="315" ht="34" customHeight="1">
       <c r="A315" s="3" t="n">
         <v>311</v>
       </c>
@@ -14813,7 +14844,7 @@
         </is>
       </c>
     </row>
-    <row r="316">
+    <row r="316" ht="34" customHeight="1">
       <c r="A316" s="3" t="n">
         <v>312</v>
       </c>
@@ -14893,7 +14924,7 @@
         </is>
       </c>
     </row>
-    <row r="318">
+    <row r="318" ht="34" customHeight="1">
       <c r="A318" s="3" t="n">
         <v>314</v>
       </c>
@@ -15133,7 +15164,7 @@
         </is>
       </c>
     </row>
-    <row r="324">
+    <row r="324" ht="34" customHeight="1">
       <c r="A324" s="3" t="n">
         <v>320</v>
       </c>
@@ -15213,7 +15244,7 @@
         </is>
       </c>
     </row>
-    <row r="326">
+    <row r="326" ht="34" customHeight="1">
       <c r="A326" s="3" t="n">
         <v>322</v>
       </c>
@@ -15293,7 +15324,7 @@
         </is>
       </c>
     </row>
-    <row r="328">
+    <row r="328" ht="34" customHeight="1">
       <c r="A328" s="3" t="n">
         <v>324</v>
       </c>
@@ -15613,7 +15644,7 @@
         </is>
       </c>
     </row>
-    <row r="336">
+    <row r="336" ht="34" customHeight="1">
       <c r="A336" s="3" t="n">
         <v>332</v>
       </c>
@@ -16173,7 +16204,7 @@
         </is>
       </c>
     </row>
-    <row r="350">
+    <row r="350" ht="34" customHeight="1">
       <c r="A350" s="3" t="n">
         <v>346</v>
       </c>
@@ -16213,7 +16244,7 @@
         </is>
       </c>
     </row>
-    <row r="351">
+    <row r="351" ht="34" customHeight="1">
       <c r="A351" s="3" t="n">
         <v>347</v>
       </c>
@@ -16893,7 +16924,7 @@
         </is>
       </c>
     </row>
-    <row r="368">
+    <row r="368" ht="34" customHeight="1">
       <c r="A368" s="3" t="n">
         <v>364</v>
       </c>
@@ -17173,7 +17204,7 @@
         </is>
       </c>
     </row>
-    <row r="375">
+    <row r="375" ht="34" customHeight="1">
       <c r="A375" s="3" t="n">
         <v>371</v>
       </c>
@@ -17213,7 +17244,7 @@
         </is>
       </c>
     </row>
-    <row r="376">
+    <row r="376" ht="34" customHeight="1">
       <c r="A376" s="3" t="n">
         <v>372</v>
       </c>
@@ -17293,7 +17324,7 @@
         </is>
       </c>
     </row>
-    <row r="378">
+    <row r="378" ht="34" customHeight="1">
       <c r="A378" s="3" t="n">
         <v>374</v>
       </c>
@@ -17493,7 +17524,7 @@
         </is>
       </c>
     </row>
-    <row r="383">
+    <row r="383" ht="34" customHeight="1">
       <c r="A383" s="3" t="n">
         <v>379</v>
       </c>
@@ -17533,7 +17564,7 @@
         </is>
       </c>
     </row>
-    <row r="384">
+    <row r="384" ht="34" customHeight="1">
       <c r="A384" s="3" t="n">
         <v>380</v>
       </c>
@@ -17613,7 +17644,7 @@
         </is>
       </c>
     </row>
-    <row r="386">
+    <row r="386" ht="34" customHeight="1">
       <c r="A386" s="3" t="n">
         <v>382</v>
       </c>
@@ -18053,7 +18084,7 @@
         </is>
       </c>
     </row>
-    <row r="397">
+    <row r="397" ht="34" customHeight="1">
       <c r="A397" s="3" t="n">
         <v>393</v>
       </c>
@@ -18173,7 +18204,7 @@
         </is>
       </c>
     </row>
-    <row r="400">
+    <row r="400" ht="34" customHeight="1">
       <c r="A400" s="3" t="n">
         <v>396</v>
       </c>
@@ -18213,7 +18244,7 @@
         </is>
       </c>
     </row>
-    <row r="401">
+    <row r="401" ht="34" customHeight="1">
       <c r="A401" s="3" t="n">
         <v>397</v>
       </c>
@@ -18253,7 +18284,7 @@
         </is>
       </c>
     </row>
-    <row r="402">
+    <row r="402" ht="34" customHeight="1">
       <c r="A402" s="3" t="n">
         <v>398</v>
       </c>
@@ -18293,7 +18324,7 @@
         </is>
       </c>
     </row>
-    <row r="403">
+    <row r="403" ht="34" customHeight="1">
       <c r="A403" s="3" t="n">
         <v>399</v>
       </c>
@@ -18333,7 +18364,7 @@
         </is>
       </c>
     </row>
-    <row r="404">
+    <row r="404" ht="34" customHeight="1">
       <c r="A404" s="3" t="n">
         <v>400</v>
       </c>
@@ -18373,7 +18404,7 @@
         </is>
       </c>
     </row>
-    <row r="405">
+    <row r="405" ht="34" customHeight="1">
       <c r="A405" s="3" t="n">
         <v>401</v>
       </c>
@@ -18413,7 +18444,7 @@
         </is>
       </c>
     </row>
-    <row r="406">
+    <row r="406" ht="34" customHeight="1">
       <c r="A406" s="3" t="n">
         <v>402</v>
       </c>
@@ -18453,7 +18484,7 @@
         </is>
       </c>
     </row>
-    <row r="407">
+    <row r="407" ht="34" customHeight="1">
       <c r="A407" s="3" t="n">
         <v>403</v>
       </c>
@@ -18505,7 +18536,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E84"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -18514,7 +18545,7 @@
     <col width="52" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>활동 · 수면 목표 문구 (지식DB 78개 + 기본 문구)</t>
@@ -18528,6 +18559,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>

--- a/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
+++ b/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
@@ -866,7 +866,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>거의 같음 / 1~2시간 / 2시간 이상</t>
+          <t>거의 같음 / 1~2시간 차이남 / 그 이상 차이남</t>
         </is>
       </c>
       <c r="G13" s="3" t="n"/>
@@ -2258,14 +2258,14 @@
           <t>거의 같음</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>1~2시간</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>2시간 이상</t>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>1~2시간 차이남</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>그 이상 차이남</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -2278,7 +2278,7 @@
         <v>32</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" ht="34" customHeight="1">

--- a/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
+++ b/docs/화면/10_홈탭/maiReport_홈_오늘의질문_문구_v1.0.0.xlsx
@@ -928,7 +928,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>거의 같음 / 1~2시간 / 2시간 이상</t>
+          <t>거의 같음 / 1~2시간 차이남 / 그 이상 차이남</t>
         </is>
       </c>
       <c r="G15" s="3" t="n"/>
@@ -2352,14 +2352,14 @@
           <t>거의 같음</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>1~2시간</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>2시간 이상</t>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>1~2시간 차이남</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>그 이상 차이남</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -2372,7 +2372,7 @@
         <v>27</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
